--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF5EAAB-181A-804B-9561-24284D4D3050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA67184-72DE-FD4F-A966-A9BE71CC740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16940" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16940" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="114">
   <si>
     <t>Software</t>
   </si>
@@ -367,6 +367,18 @@
   </si>
   <si>
     <t>Kundli Chakra Professional</t>
+  </si>
+  <si>
+    <t>Icecream Screen Recorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WinRAR Professional </t>
+  </si>
+  <si>
+    <t>MiniTool Power Data Recovery 2026</t>
+  </si>
+  <si>
+    <t>EaseUS Data Recovery Wizard Technician</t>
   </si>
 </sst>
 </file>
@@ -442,11 +454,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -781,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4B76ED-CF2B-0D46-BCA1-852CF354D9D5}">
-  <dimension ref="A1:A102"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
@@ -1295,6 +1310,26 @@
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA67184-72DE-FD4F-A966-A9BE71CC740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B4EA1B-48E9-2540-990B-F1B7E723361F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16940" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
   <si>
     <t>Software</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>EaseUS Data Recovery Wizard Technician</t>
+  </si>
+  <si>
+    <t>Autocad 2027</t>
   </si>
 </sst>
 </file>
@@ -796,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4B76ED-CF2B-0D46-BCA1-852CF354D9D5}">
-  <dimension ref="A1:A106"/>
+  <dimension ref="A1:A107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
@@ -1332,6 +1335,11 @@
         <v>113</v>
       </c>
     </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1340,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88BB426D-FBED-3542-BD04-64E6FFCD9253}">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
@@ -1746,6 +1754,11 @@
         <v>108</v>
       </c>
     </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B4EA1B-48E9-2540-990B-F1B7E723361F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECEDD8A-0C5B-EA41-A03E-41F26166F25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="116">
   <si>
     <t>Software</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>Autocad 2027</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -465,6 +468,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,88 +803,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4B76ED-CF2B-0D46-BCA1-852CF354D9D5}">
-  <dimension ref="A1:A107"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1285,59 +1293,62 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>114</v>
+      </c>
+      <c r="B107" s="5">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -1348,88 +1359,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88BB426D-FBED-3542-BD04-64E6FFCD9253}">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1754,9 +1769,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>114</v>
+      </c>
+      <c r="B81" s="5">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECEDD8A-0C5B-EA41-A03E-41F26166F25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B063D9E-8CD3-A641-8731-EBF13F9C7924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="117">
   <si>
     <t>Software</t>
   </si>
@@ -384,7 +384,10 @@
     <t>Autocad 2027</t>
   </si>
   <si>
-    <t>Price</t>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Latest</t>
   </si>
 </sst>
 </file>
@@ -1347,8 +1350,8 @@
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="5">
-        <v>2000</v>
+      <c r="B107" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1773,8 +1776,8 @@
       <c r="A81" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="5">
-        <v>10000</v>
+      <c r="B81" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B063D9E-8CD3-A641-8731-EBF13F9C7924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EF3020-D6CB-AB40-935B-7D72B81EF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
   <si>
     <t>Software</t>
   </si>
@@ -1136,82 +1136,85 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B71" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>79</v>
       </c>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EF3020-D6CB-AB40-935B-7D72B81EF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22D535E-8335-3941-B0EB-02267DFB9702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
   <si>
     <t>Software</t>
   </si>
@@ -388,13 +388,19 @@
   </si>
   <si>
     <t>Latest</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>www.youtube.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -420,6 +426,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -460,10 +474,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -472,8 +487,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -806,92 +823,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4B76ED-CF2B-0D46-BCA1-852CF354D9D5}">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="3" max="3" width="63.83203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1358,6 +1382,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B3BC29F9-7458-544D-BD0D-890D56F499F9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1365,92 +1392,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88BB426D-FBED-3542-BD04-64E6FFCD9253}">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="3" max="3" width="51.1640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22D535E-8335-3941-B0EB-02267DFB9702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47CEFC9-188F-804D-9EBE-66204DECDB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" activeTab="1" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="16920" xr2:uid="{348E5074-3515-0B4A-AB07-E04CD59ECA3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="120">
   <si>
     <t>Software</t>
   </si>
@@ -393,7 +393,10 @@
     <t>Link</t>
   </si>
   <si>
-    <t>www.youtube.com</t>
+    <t>https://www.youtube.com/</t>
+  </si>
+  <si>
+    <t>https://www.microsoft.com/en-in</t>
   </si>
 </sst>
 </file>
@@ -854,6 +857,9 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="C3" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -1384,6 +1390,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{B3BC29F9-7458-544D-BD0D-890D56F499F9}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{AE9FAE3E-011C-7B4B-A098-10D70B727B99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashish Kumar\Downloads\Compressed\quicksoftwares-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Quick Softwares\Website\quicksoftwares-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927FE0B8-DFEA-496E-BCA3-C8E9E63DB1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6021A5-9AA9-4BF0-A0D2-5D2732A4C080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="13350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="124">
   <si>
     <t>Software</t>
   </si>
@@ -41,18 +41,12 @@
     <t>Autocad 2026</t>
   </si>
   <si>
-    <t>https://www.youtube.com/</t>
-  </si>
-  <si>
     <t>Autodesk softwares at ₹7,500 each</t>
   </si>
   <si>
     <t>Autocad 2024</t>
   </si>
   <si>
-    <t>https://www.microsoft.com/en-in</t>
-  </si>
-  <si>
     <t>3ds Max 2026</t>
   </si>
   <si>
@@ -393,6 +387,12 @@
   </si>
   <si>
     <t>Smart PLS 4</t>
+  </si>
+  <si>
+    <t>3ds Max 2025</t>
+  </si>
+  <si>
+    <t>Revit 2023</t>
   </si>
 </sst>
 </file>
@@ -869,27 +869,23 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="C2" s="4"/>
       <c r="D2" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2">
         <v>1500</v>
@@ -897,7 +893,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="D5" s="2">
         <v>1500</v>
@@ -905,7 +901,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2">
         <v>1500</v>
@@ -913,7 +909,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2">
         <v>1500</v>
@@ -921,7 +917,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="D8" s="2">
         <v>1500</v>
@@ -929,7 +925,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
         <v>1500</v>
@@ -937,7 +933,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2">
         <v>1500</v>
@@ -945,7 +941,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2">
         <v>1500</v>
@@ -953,7 +949,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
         <v>1500</v>
@@ -961,7 +957,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
         <v>1500</v>
@@ -969,7 +965,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2">
         <v>1500</v>
@@ -977,7 +973,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2">
         <v>1500</v>
@@ -985,7 +981,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2">
         <v>1500</v>
@@ -993,7 +989,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="2">
         <v>1500</v>
@@ -1001,7 +997,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2">
         <v>1500</v>
@@ -1009,7 +1005,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2">
         <v>1500</v>
@@ -1017,7 +1013,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2">
         <v>1500</v>
@@ -1025,7 +1021,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="2">
         <v>1500</v>
@@ -1033,7 +1029,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2">
         <v>1500</v>
@@ -1041,7 +1037,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" s="2">
         <v>1500</v>
@@ -1049,7 +1045,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2">
         <v>1500</v>
@@ -1057,7 +1053,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2">
         <v>1500</v>
@@ -1065,7 +1061,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2">
         <v>1500</v>
@@ -1073,7 +1069,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2">
         <v>1500</v>
@@ -1081,7 +1077,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" s="2">
         <v>1500</v>
@@ -1089,7 +1085,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2">
         <v>1500</v>
@@ -1097,7 +1093,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="2">
         <v>1500</v>
@@ -1105,7 +1101,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
         <v>1500</v>
@@ -1113,7 +1109,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2">
         <v>1500</v>
@@ -1121,7 +1117,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
         <v>1500</v>
@@ -1129,7 +1125,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2">
         <v>1500</v>
@@ -1137,7 +1133,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2">
         <v>1500</v>
@@ -1145,7 +1141,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
         <v>1500</v>
@@ -1153,7 +1149,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" s="2">
         <v>1500</v>
@@ -1161,7 +1157,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
         <v>1500</v>
@@ -1169,7 +1165,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D39" s="2">
         <v>1500</v>
@@ -1177,7 +1173,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" s="2">
         <v>1500</v>
@@ -1185,7 +1181,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2">
         <v>1500</v>
@@ -1193,7 +1189,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2">
         <v>1500</v>
@@ -1201,7 +1197,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D43" s="2">
         <v>1500</v>
@@ -1209,7 +1205,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D44" s="2">
         <v>1500</v>
@@ -1217,7 +1213,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2">
         <v>1500</v>
@@ -1225,7 +1221,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2">
         <v>1500</v>
@@ -1233,7 +1229,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D47" s="2">
         <v>1500</v>
@@ -1241,7 +1237,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2">
         <v>1500</v>
@@ -1249,7 +1245,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2">
         <v>1500</v>
@@ -1257,7 +1253,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2">
         <v>1500</v>
@@ -1265,7 +1261,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2">
         <v>1500</v>
@@ -1273,7 +1269,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2">
         <v>1500</v>
@@ -1281,7 +1277,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2">
         <v>1500</v>
@@ -1289,7 +1285,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D54" s="2">
         <v>1500</v>
@@ -1297,7 +1293,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2">
         <v>1500</v>
@@ -1305,7 +1301,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D56" s="2">
         <v>1500</v>
@@ -1313,7 +1309,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2">
         <v>1500</v>
@@ -1321,7 +1317,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D58" s="2">
         <v>1500</v>
@@ -1329,7 +1325,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D59" s="2">
         <v>1500</v>
@@ -1337,7 +1333,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D60" s="2">
         <v>1500</v>
@@ -1345,7 +1341,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D61" s="2">
         <v>1500</v>
@@ -1353,7 +1349,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D62" s="2">
         <v>1500</v>
@@ -1361,7 +1357,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D63" s="2">
         <v>1500</v>
@@ -1369,7 +1365,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D64" s="2">
         <v>1500</v>
@@ -1377,7 +1373,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D65" s="2">
         <v>1500</v>
@@ -1385,7 +1381,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D66" s="2">
         <v>1500</v>
@@ -1393,7 +1389,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D67" s="2">
         <v>1500</v>
@@ -1401,7 +1397,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D68" s="2">
         <v>1500</v>
@@ -1409,7 +1405,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D69" s="2">
         <v>1500</v>
@@ -1417,7 +1413,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D70" s="2">
         <v>1500</v>
@@ -1425,10 +1421,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D71" s="2">
         <v>1500</v>
@@ -1436,7 +1432,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2">
         <v>1500</v>
@@ -1444,7 +1440,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D73" s="2">
         <v>1500</v>
@@ -1452,7 +1448,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D74" s="2">
         <v>1500</v>
@@ -1460,7 +1456,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D75" s="2">
         <v>1500</v>
@@ -1468,7 +1464,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D76" s="2">
         <v>1500</v>
@@ -1476,7 +1472,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D77" s="2">
         <v>1500</v>
@@ -1484,7 +1480,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D78" s="2">
         <v>1500</v>
@@ -1492,7 +1488,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D79" s="2">
         <v>1500</v>
@@ -1500,7 +1496,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D80" s="2">
         <v>1500</v>
@@ -1508,7 +1504,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D81" s="2">
         <v>1500</v>
@@ -1516,7 +1512,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D82" s="2">
         <v>1500</v>
@@ -1524,7 +1520,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D83" s="2">
         <v>1500</v>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D84" s="2">
         <v>1500</v>
@@ -1540,7 +1536,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D85" s="2">
         <v>1500</v>
@@ -1548,7 +1544,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D86" s="2">
         <v>1500</v>
@@ -1556,7 +1552,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D87" s="2">
         <v>1500</v>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D88" s="2">
         <v>1500</v>
@@ -1572,7 +1568,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D89" s="2">
         <v>1500</v>
@@ -1580,7 +1576,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D90" s="2">
         <v>1500</v>
@@ -1588,7 +1584,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D91" s="2">
         <v>1500</v>
@@ -1596,7 +1592,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D92" s="2">
         <v>1500</v>
@@ -1604,7 +1600,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D93" s="2">
         <v>1500</v>
@@ -1612,7 +1608,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D94" s="2">
         <v>1500</v>
@@ -1620,7 +1616,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D95" s="2">
         <v>1500</v>
@@ -1628,7 +1624,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D96" s="2">
         <v>1500</v>
@@ -1636,7 +1632,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D97" s="2">
         <v>1500</v>
@@ -1644,7 +1640,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D98" s="2">
         <v>1500</v>
@@ -1652,7 +1648,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D99" s="2">
         <v>1500</v>
@@ -1660,7 +1656,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D100" s="2">
         <v>1500</v>
@@ -1668,7 +1664,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D101" s="2">
         <v>1500</v>
@@ -1676,7 +1672,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D102" s="2">
         <v>1500</v>
@@ -1684,7 +1680,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D103" s="2">
         <v>1500</v>
@@ -1692,7 +1688,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D104" s="2">
         <v>1500</v>
@@ -1700,7 +1696,7 @@
     </row>
     <row r="105" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D105" s="2">
         <v>1500</v>
@@ -1708,7 +1704,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D106" s="2">
         <v>1500</v>
@@ -1716,10 +1712,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D107" s="2">
         <v>1500</v>
@@ -1727,14 +1723,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1778,133 +1770,133 @@
         <v>7500</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3">
         <v>7500</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3">
         <v>7500</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>7500</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3">
         <v>7500</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3">
         <v>7500</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3">
         <v>7500</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="3">
         <v>7500</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3">
         <v>7500</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3">
         <v>7500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3">
         <v>7500</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3">
         <v>7500</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3">
         <v>2500</v>
@@ -1912,7 +1904,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3">
         <v>2500</v>
@@ -1920,7 +1912,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3">
         <v>2500</v>
@@ -1928,7 +1920,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="3">
         <v>2500</v>
@@ -1936,7 +1928,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3">
         <v>2500</v>
@@ -1944,7 +1936,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" s="3">
         <v>2500</v>
@@ -1952,7 +1944,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3">
         <v>2500</v>
@@ -1960,7 +1952,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3">
         <v>2500</v>
@@ -1968,7 +1960,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3">
         <v>2500</v>
@@ -1976,7 +1968,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" s="3">
         <v>2500</v>
@@ -1984,7 +1976,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="3">
         <v>2500</v>
@@ -1992,7 +1984,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3">
         <v>2500</v>
@@ -2000,7 +1992,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="3">
         <v>2500</v>
@@ -2008,7 +2000,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="3">
         <v>2500</v>
@@ -2016,7 +2008,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" s="3">
         <v>2500</v>
@@ -2024,7 +2016,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="3">
         <v>2500</v>
@@ -2032,7 +2024,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="3">
         <v>2500</v>
@@ -2040,7 +2032,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3">
         <v>2500</v>
@@ -2048,7 +2040,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" s="3">
         <v>2500</v>
@@ -2056,7 +2048,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" s="3">
         <v>2500</v>
@@ -2064,7 +2056,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3">
         <v>2500</v>
@@ -2072,7 +2064,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" s="3">
         <v>2500</v>
@@ -2080,7 +2072,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D36" s="3">
         <v>2500</v>
@@ -2088,7 +2080,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" s="3">
         <v>2500</v>
@@ -2096,7 +2088,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D38" s="3">
         <v>2500</v>
@@ -2104,7 +2096,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D39" s="3">
         <v>2500</v>
@@ -2112,7 +2104,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3">
         <v>2500</v>
@@ -2120,7 +2112,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D41" s="3">
         <v>2500</v>
@@ -2128,7 +2120,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D42" s="3">
         <v>2500</v>
@@ -2136,7 +2128,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D43" s="3">
         <v>2500</v>
@@ -2144,7 +2136,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D44" s="3">
         <v>2500</v>
@@ -2152,7 +2144,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D45" s="3">
         <v>2500</v>
@@ -2160,7 +2152,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D46" s="3">
         <v>2500</v>
@@ -2168,7 +2160,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D47" s="3">
         <v>2500</v>
@@ -2176,7 +2168,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D48" s="3">
         <v>2500</v>
@@ -2184,7 +2176,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D49" s="3">
         <v>2500</v>
@@ -2192,7 +2184,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D50" s="3">
         <v>2500</v>
@@ -2200,7 +2192,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D51" s="3">
         <v>2500</v>
@@ -2208,7 +2200,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D52" s="3">
         <v>2500</v>
@@ -2216,7 +2208,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D53" s="3">
         <v>2500</v>
@@ -2224,7 +2216,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D54" s="3">
         <v>2500</v>
@@ -2232,7 +2224,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D55" s="3">
         <v>2500</v>
@@ -2240,7 +2232,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D56" s="3">
         <v>2500</v>
@@ -2248,7 +2240,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D57" s="3">
         <v>2500</v>
@@ -2256,7 +2248,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D58" s="3">
         <v>2500</v>
@@ -2264,7 +2256,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3">
         <v>2500</v>
@@ -2272,7 +2264,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D60" s="3">
         <v>2500</v>
@@ -2280,7 +2272,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D61" s="3">
         <v>2500</v>
@@ -2288,7 +2280,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D62" s="3">
         <v>2500</v>
@@ -2296,7 +2288,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D63" s="3">
         <v>2500</v>
@@ -2304,7 +2296,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D64" s="3">
         <v>2500</v>
@@ -2312,7 +2304,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D65" s="3">
         <v>2500</v>
@@ -2320,7 +2312,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D66" s="3">
         <v>2500</v>
@@ -2328,7 +2320,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D67" s="3">
         <v>2500</v>
@@ -2336,7 +2328,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D68" s="3">
         <v>2500</v>
@@ -2344,7 +2336,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D69" s="3">
         <v>2500</v>
@@ -2352,7 +2344,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D70" s="3">
         <v>2500</v>
@@ -2360,7 +2352,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D71" s="3">
         <v>2500</v>
@@ -2368,7 +2360,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D72" s="3">
         <v>2500</v>
@@ -2376,7 +2368,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D73" s="3">
         <v>2500</v>
@@ -2384,7 +2376,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D74" s="3">
         <v>2500</v>
@@ -2392,7 +2384,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D75" s="3">
         <v>2500</v>
@@ -2400,7 +2392,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D76" s="3">
         <v>2500</v>
@@ -2408,7 +2400,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D77" s="3">
         <v>2500</v>
@@ -2416,7 +2408,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3">
         <v>2500</v>
@@ -2424,38 +2416,38 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D79" s="3">
         <v>7500</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D80" s="3">
         <v>7500</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D81" s="3">
         <v>7500</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Quick Softwares\Website\quicksoftwares-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6021A5-9AA9-4BF0-A0D2-5D2732A4C080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AFA41E-BD41-47AF-B195-EADF221030F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="13350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="13350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06393998-9167-924A-B751-099B60F21CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B7EE34-59BA-C84D-93EF-DF53A164EBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="136">
   <si>
     <t>Software</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Little Snitch</t>
   </si>
   <si>
-    <t>CleanMyMac</t>
-  </si>
-  <si>
     <t>Final Cut Pro</t>
   </si>
   <si>
@@ -218,26 +215,229 @@
     <t xml:space="preserve">Autodesk Autocad </t>
   </si>
   <si>
-    <t>Lumion Pro (Parallel Desktop only)</t>
-  </si>
-  <si>
-    <t>Autodesk Navis Work</t>
+    <t>https://transfer.it/t/tKKapBklxTKK</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/5raK4QshhbZS</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/Lr6fKckxWJhY</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/562drlc3lsayh9g/Adobe+Photoshop+2026+v27.8.0.tar.001/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/4jrvk4wvgxqozue/Adobe_Illustrator_2026_v30.4.0.226.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/jj4zc2k8j7fgzpo/Adobe_Premiere_Pro_2026_v26.3_(x64).tar.001/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/szicm7sha1cfbh1/Adobe-After-Effects+2026+v26.3.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/6vsjv39afiac37x/Adobe_InDesign_2026_v21.4_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/t4i070w34hm7yhk/Adobe_Media_Encoder_2026_v26.3.tar.001/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/dy4327sw4c74fn9/Adobe-Acrobat-Pro-DC+2026+V26.1.21677+(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/2iuzlwzulabyp1q/Adobe_XD_v61.0.12.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/fz0hr8b7dyn72qy/Adobe_Audition_2026_v26.3_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/m2e45t89wzsueu1/Adobe-Lightroom-Classic+2026+v15.4.1+(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/nxk93sn95mb087w/ARCHITECTURE_2026.0.1_ADDON_FOR_AUTODESK_AUTOCAD.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/noede2v600ahqea/Adobe_Animate_2024_24.0.12.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/u50w0ad5ni7jzxo/Adobe_Bridge_2026_v16.0.4_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/1v22irqpqhhfyu3/ADOBE_DREAMWEAVER_2021_21.6.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/sp1ycv7803y3q0d/Adobe.Premiere.Rush.v2.10.Multilingual.exe/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/xf86206xqj39vtr/Adobe_Dimension_4.1.8_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/kwpbudvo54cio0a/Adobe_InCopy_2026_v21.4_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/ofs743ut01470s9/CorelDRAW+Graphics+Suite+2026+27.1.0.129.7z/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/xu4o0y4u4l2yuhu/Wondershare+Filmora+15.5.3.19727+(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/bbeml0ghckc6z0f/CapCut_6.6.0.2586.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/x4u3co6wnrmjwfx/Nitro-PDF-Pro+26.1.0.54+(x64)+Enterprise.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/fmnn4r4a18ou03r/SketchUp-Pro+2026+v26.2.243+(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/iq7mqfq0fey39hh/Chaos_V-Ray_7.40.00_for_SketchUp.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/1ib0odtz2tk2i3v/Blender_4.4.3_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/f24sy8w6ydefwc4/Microsoft-Office-2024-LTSC-v2408+Build+17932.20884+(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/a5url0w26v1pz59/NCH_Debut_Professional_12.05.tar/file</t>
+  </si>
+  <si>
+    <t>https://94-130-167-220.top/Getintopc.com/Mastercam_2026_v28.0.7534.rar?md5=yGM16QDKmpvMK5O-ReA48A&amp;expires=1787806465</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/Aeb5S45BBT5D                             and                        https://transfer.it/t/88Xpj6wD1TwJ</t>
+  </si>
+  <si>
+    <t>https://94-130-16-162.top/Getintopc.com/GRAPHISOFT_ArchiCAD_29_Build_3000.rar?md5=PZCPx58Jc0wzlTdJU9Oj-Q&amp;expires=1787806945</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/q2av0w2f4er4v9c/ZWCADProfessional2024SP1Build2023.10.31x64.zip/file</t>
+  </si>
+  <si>
+    <t>https://94-130-167-220.top/Getintopc.com/SolidWorks_2026_SP0_Full_Premium_Multilingual-03-01-2026.rar?md5=DltAdCdaOTlYQKz2WHSCMg&amp;expires=1787807079</t>
+  </si>
+  <si>
+    <t>https://88-99-218-153.top/Getintopc.com/AutoCAD_Architecture_2024_English_Win_64-bit.iso?md5=1TqeAaVel39OXDzWpTLj8w&amp;expires=1787807466</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/zdkj7h58sjwkjem/Rhinoceros_8.8.24170.13001.7z/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/93b254yd5eelkm3/Chaos_Enscape_4.18.1.1579_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/ga9czz0k3f187a1/Chaos_V-Ray_7.40.00_for_Rhinoceros.tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/d3gfy2kjsu3u3u7/Corona_Renderer_11_Hotfix_2_for_3DS_MAX_2016-2025.7z/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/il5azr6sqsj2vxc/WinRAR_7.23_Final_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://www.mediafire.com/file/a6oq6baae1znmoi/Icecream_Screen_Recorder_Pro_7.48_(x64).tar/file</t>
+  </si>
+  <si>
+    <t>https://94-130-16-162.top/Getintopc.com/Siemens_Solid_Edge_2025.2410.rar?md5=SnaNUiOIAOYjAHoUw7zdlg&amp;expires=1787808105</t>
+  </si>
+  <si>
+    <t>https://88-99-162-81.top/Getintopc.com/Gemvision_MatrixGold_v.3.1.22284.1001.rar?md5=q2MYmz-sXT8_RGA42lYJTw&amp;expires=1787808160</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/2BHPHjhXkJqT</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/qa0Oy6pHVDBR</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/tjzX22hxXTaY</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/0dTAvv5hnBDJ</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/x7PttZkzFLqL</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/qpcONRljEZKK</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/OfmCBY9T2TKC</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/i6AmhF8RSbyI</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/CvsIgd9BlJAb</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/H3clBB53hRSR</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/hI68FdsnGDjA</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/olbK9R0XTDIT</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/FIiH1I1nAZqR</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/vfK8cZsBFTyR</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/6xRNNFsFEDqI</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/z4kLVUs3TJyC</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/jFqLUYlxmLbb</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/eMOm0YknUbpR</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/6BXWIJ0TXbiI</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/PbvlJFsTXbDa</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/GIheAY1R3bxT</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/X53UcNlR3JKK</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/LWP6cihnmboI</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/GIZ74z4FwZ6A</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/4roT07olxDrL</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/C5jCNv5FmRTA</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/HXbXNvolSBZQ</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/N8R4Q2oV1b7b</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/feTGp35lHLiB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -252,29 +452,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -319,15 +511,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -664,464 +857,656 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2"/>
-    <col min="5" max="5" width="29.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11" style="2"/>
+    <col min="1" max="1" width="27.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="140.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="C15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="C17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="C18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="C23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="C27" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="C30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="C32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="C33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="C35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="C36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="2">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="2">
+      <c r="C37" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="2">
+      <c r="C38" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="2">
+      <c r="C39" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="2">
+      <c r="C40" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="2">
+      <c r="C43" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="2">
+      <c r="C46" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="2">
+      <c r="C47" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="2">
+      <c r="C48" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="2">
+      <c r="C49" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="2">
+      <c r="C50" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="2">
+      <c r="C51" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="2">
+      <c r="C53" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="2">
+      <c r="C54" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>38</v>
+      <c r="A55" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{69C9B440-76F5-AE4D-A252-140241995CCB}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{4D015B6F-E1ED-DE42-89BA-34B02D5A46E1}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{CCD155F7-7751-1645-9753-7BF1CC30A197}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{2EC4EAE3-9B4A-B64A-9F2B-F8E23B60644B}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{57BEE593-96E3-4C46-B389-616BEB309A0D}"/>
+    <hyperlink ref="C9" r:id="rId6" xr:uid="{C70D749E-3AF6-114B-A7EB-34BC45B28815}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{A817844E-17FD-8944-835A-85225DEA4B1B}"/>
+    <hyperlink ref="C11" r:id="rId8" xr:uid="{D8C94F38-845F-2248-A206-474537A02ED8}"/>
+    <hyperlink ref="C12" r:id="rId9" xr:uid="{91AA6801-5070-7A43-840E-B68B3AA5D340}"/>
+    <hyperlink ref="C15" r:id="rId10" xr:uid="{FAB93B04-5A8E-6C44-B0AD-B96C4CE4A054}"/>
+    <hyperlink ref="C14" r:id="rId11" xr:uid="{248C0ED6-0FC3-154A-9B51-82B8E27290C9}"/>
+    <hyperlink ref="C16" r:id="rId12" xr:uid="{0B383DD1-B844-2741-B768-8A067E2463F6}"/>
+    <hyperlink ref="C13" r:id="rId13" xr:uid="{A3FACD8D-41C3-764D-8B1D-F30AD4142414}"/>
+    <hyperlink ref="C6" r:id="rId14" xr:uid="{E88A894F-5D58-9849-A127-C48C0C5D9DE3}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{32D1D782-2CE4-4A4E-A44A-B06866356971}"/>
+    <hyperlink ref="C18" r:id="rId16" xr:uid="{D5A00063-22C1-EE41-8853-5E419BEA9C7A}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{2DE15994-9F43-8348-9727-7EF6FA3B6171}"/>
+    <hyperlink ref="C21" r:id="rId18" xr:uid="{4CEBE21B-0487-2846-9ABA-29E54E602D68}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{603CAB2A-435B-744A-BA3E-3FBCB27E044C}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{E8CFFB1D-E082-9041-BF41-0716BF8D9521}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{37A93B78-F327-5D47-8E6C-615651A377D2}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{E2CD50EC-592C-404F-AEB6-958AC54C7DA9}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{F0E098EC-53A8-5C43-9C36-5A86FCC1AB5C}"/>
+    <hyperlink ref="C27" r:id="rId24" xr:uid="{880971D2-BA24-F54C-B12D-54F1235F5FB1}"/>
+    <hyperlink ref="C40" r:id="rId25" xr:uid="{C62D5616-246C-144D-ABA8-B8092B2B07F9}"/>
+    <hyperlink ref="C28" r:id="rId26" xr:uid="{BB88705D-2E09-4947-A008-EB0CA6931C97}"/>
+    <hyperlink ref="C30" r:id="rId27" xr:uid="{392FF531-073A-0C46-A6EC-18DE290D8FC1}"/>
+    <hyperlink ref="C31" r:id="rId28" xr:uid="{8667D7BE-C9E3-874B-A1AD-0B586BDCE93E}"/>
+    <hyperlink ref="C29" r:id="rId29" xr:uid="{B72876AB-0F3F-B74E-82A9-8E10775A75D6}"/>
+    <hyperlink ref="C32" r:id="rId30" xr:uid="{DC703474-1DAF-C34E-9FDD-32ED157AA192}"/>
+    <hyperlink ref="C33" r:id="rId31" display="https://transfer.it/t/Aeb5S45BBT5Dhttps://transfer.it/t/88Xpj6wD1TwJ" xr:uid="{E2171A18-4734-8B49-9EAB-65A1CF063EE6}"/>
+    <hyperlink ref="C34" r:id="rId32" xr:uid="{F720F81E-5D6C-7D4F-A28D-6AC27B9B9AF7}"/>
+    <hyperlink ref="C35" r:id="rId33" xr:uid="{A6E84F36-D06D-A248-ADDA-0BE0E4535B93}"/>
+    <hyperlink ref="C36" r:id="rId34" xr:uid="{74949948-8B2D-A547-97AA-4F134F25A597}"/>
+    <hyperlink ref="C5" r:id="rId35" xr:uid="{4567DE7B-D153-3A46-A9EA-3DBF16101B65}"/>
+    <hyperlink ref="C39" r:id="rId36" xr:uid="{21DDF167-1C2D-C34C-B9D1-70578BD676E5}"/>
+    <hyperlink ref="C46" r:id="rId37" xr:uid="{2D96803E-1F4A-F144-B377-13FCD4481B6B}"/>
+    <hyperlink ref="C47" r:id="rId38" xr:uid="{035EBE33-E4A0-DD47-AEE6-290DE7F6B7E1}"/>
+    <hyperlink ref="C48" r:id="rId39" xr:uid="{2E62AF53-D19E-3E44-8B37-5B55926A5F49}"/>
+    <hyperlink ref="C43" r:id="rId40" xr:uid="{DE183AC8-C69C-4146-A2C1-EC6F40FD4908}"/>
+    <hyperlink ref="C49" r:id="rId41" xr:uid="{D8B3FBDF-ACCB-B74E-9565-328E6A504368}"/>
+    <hyperlink ref="C54" r:id="rId42" xr:uid="{E6D02673-988B-584F-9883-542ACE57C315}"/>
+    <hyperlink ref="C53" r:id="rId43" xr:uid="{A69A2E29-66AC-D84F-B0B2-5CF665403865}"/>
+    <hyperlink ref="C37" r:id="rId44" xr:uid="{EADE3535-FF21-6048-8674-1A1D733E5069}"/>
+    <hyperlink ref="C38" r:id="rId45" xr:uid="{C8C07313-A8E7-5449-A427-13B902850BC2}"/>
+    <hyperlink ref="C50" r:id="rId46" xr:uid="{8C2C2479-9F37-9B45-864F-B531C6BA1492}"/>
+    <hyperlink ref="C51" r:id="rId47" xr:uid="{BDD96A07-7960-9745-8B89-16BE9D2D0627}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1129,357 +1514,466 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="51.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11" style="3"/>
-    <col min="5" max="5" width="29.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11" style="3"/>
+    <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1"/>
+    <col min="5" max="5" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="3">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="4">
         <v>7500</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="4">
         <v>7500</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="B29" s="4"/>
+      <c r="C29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="3">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{4E951DC0-7FC6-B344-89E4-0D6C6AC9F675}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{3F1A632A-8FBA-3C44-B68F-09D31ACAAA6A}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{CF68CB4D-D0C4-EE4C-8B5F-D4C3E5D2899B}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{95EAC6FE-23F4-AF4F-A710-68AF050E4CDB}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{1C47183A-4BFD-9C4A-BE8C-377C619C6840}"/>
+    <hyperlink ref="C9" r:id="rId6" xr:uid="{243099B5-EF0D-DF45-B1BF-108A09D1936B}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{32D5B07C-6782-5A4D-AF93-9184ED03DC18}"/>
+    <hyperlink ref="C13" r:id="rId8" xr:uid="{A1B6A6E2-4703-5D4C-BA40-D41C44058D5A}"/>
+    <hyperlink ref="C14" r:id="rId9" xr:uid="{C6B623B5-FBF4-ED4A-BB9C-65BAE8C7AD6F}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{F3C71488-DE12-D548-9252-8BAE98E96C50}"/>
+    <hyperlink ref="C23" r:id="rId11" xr:uid="{A8EFDB8A-04BA-894C-A384-6BF3E0946C1A}"/>
+    <hyperlink ref="C30" r:id="rId12" xr:uid="{4B3119FF-4E65-2447-B7B7-ED4ED9065F86}"/>
+    <hyperlink ref="C2" r:id="rId13" xr:uid="{E6893805-78A2-384C-A3BE-66F3A9BD33F2}"/>
+    <hyperlink ref="C25" r:id="rId14" xr:uid="{A23A9765-6ADF-8448-8A36-3EC504A2FFCF}"/>
+    <hyperlink ref="C26" r:id="rId15" xr:uid="{1649EF47-F09B-FF4E-9026-C97FB4C400BA}"/>
+    <hyperlink ref="C19" r:id="rId16" xr:uid="{2E3EAC4D-57DC-1B40-9804-F09C4B5D5B81}"/>
+    <hyperlink ref="C15" r:id="rId17" xr:uid="{85E6E437-6DCB-174C-95E9-68E81739A652}"/>
+    <hyperlink ref="C3" r:id="rId18" xr:uid="{406F08FF-5225-CD46-8093-F90AA30AB7F7}"/>
+    <hyperlink ref="C16" r:id="rId19" xr:uid="{392CC729-C4BC-AB4A-A2BD-64F4B88E5242}"/>
+    <hyperlink ref="C29" r:id="rId20" xr:uid="{8A8CD341-6E3C-1B4F-97BB-727F4E8F60BC}"/>
+    <hyperlink ref="C27" r:id="rId21" xr:uid="{A44CFDB7-E809-D74F-A009-8431E52DC952}"/>
+    <hyperlink ref="C17" r:id="rId22" xr:uid="{6DFF26B2-1ADB-254E-8342-CC133E947493}"/>
+    <hyperlink ref="C11" r:id="rId23" xr:uid="{886A766F-92F1-BD40-84D8-0662D198E129}"/>
+    <hyperlink ref="C18" r:id="rId24" xr:uid="{2EF09DBB-F54F-7942-99C4-F3257E8391B4}"/>
+    <hyperlink ref="C21" r:id="rId25" xr:uid="{63374A16-2809-0447-9ED8-084790C683A8}"/>
+    <hyperlink ref="C31" r:id="rId26" xr:uid="{F4118F8F-E675-7343-9FF4-F65E04EA5C58}"/>
+    <hyperlink ref="C22" r:id="rId27" xr:uid="{95DD04B2-6AAF-C843-8206-3FCD370C7930}"/>
+    <hyperlink ref="C20" r:id="rId28" xr:uid="{86C3D4D8-951D-1D48-8BB8-8B4572B15086}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AshishKumar.Soni/quicksoftwares/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashish Kumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B7EE34-59BA-C84D-93EF-DF53A164EBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B770B5AF-7434-4D30-80CA-D4D7CAF697AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="138">
   <si>
     <t>Software</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>https://transfer.it/t/feTGp35lHLiB</t>
+  </si>
+  <si>
+    <t>https://138-201-124-163.top/Getintopc.com/Intergraph_SmartPlant_3D_2011_R1_v09.01.30.0055.rar?md5=yB-ziU1NgK90GZFfrwOGEw&amp;expires=1788147891</t>
+  </si>
+  <si>
+    <t>Smart Plant 3D</t>
   </si>
 </sst>
 </file>
@@ -517,10 +523,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -856,18 +862,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="140.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="140.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="11" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -884,7 +890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -895,7 +901,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -906,7 +912,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -917,7 +923,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -928,7 +934,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
@@ -939,7 +945,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -950,7 +956,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>44</v>
       </c>
@@ -961,7 +967,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
@@ -972,7 +978,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>46</v>
       </c>
@@ -983,7 +989,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
@@ -994,7 +1000,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
@@ -1005,7 +1011,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -1027,7 +1033,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
@@ -1038,7 +1044,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
@@ -1049,7 +1055,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
@@ -1071,7 +1077,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>7</v>
       </c>
@@ -1082,7 +1088,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>9</v>
       </c>
@@ -1104,7 +1110,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>55</v>
       </c>
@@ -1115,7 +1121,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1159,7 +1165,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>13</v>
       </c>
@@ -1181,7 +1187,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>14</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>58</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>59</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>16</v>
       </c>
@@ -1247,7 +1253,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>60</v>
       </c>
@@ -1258,7 +1264,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>61</v>
       </c>
@@ -1269,7 +1275,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>62</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -1291,7 +1297,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>18</v>
       </c>
@@ -1302,7 +1308,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>19</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>20</v>
       </c>
@@ -1321,7 +1327,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>21</v>
       </c>
@@ -1329,7 +1335,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>22</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>23</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>24</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>25</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>26</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>27</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>28</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>29</v>
       </c>
@@ -1411,7 +1417,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>30</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>31</v>
       </c>
@@ -1430,7 +1436,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>32</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>33</v>
       </c>
@@ -1452,9 +1458,17 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1506,6 +1520,7 @@
     <hyperlink ref="C38" r:id="rId45" xr:uid="{C8C07313-A8E7-5449-A427-13B902850BC2}"/>
     <hyperlink ref="C50" r:id="rId46" xr:uid="{8C2C2479-9F37-9B45-864F-B531C6BA1492}"/>
     <hyperlink ref="C51" r:id="rId47" xr:uid="{BDD96A07-7960-9745-8B89-16BE9D2D0627}"/>
+    <hyperlink ref="C56" r:id="rId48" xr:uid="{0277A29E-6A56-4860-AEEF-D8C7E0BCB95D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1515,17 +1530,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1"/>
     <col min="5" max="5" width="29.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
@@ -1557,7 +1572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -1572,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1585,7 +1600,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -1598,7 +1613,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
@@ -1611,7 +1626,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>46</v>
       </c>
@@ -1624,7 +1639,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
@@ -1637,7 +1652,7 @@
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1650,7 +1665,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
@@ -1663,7 +1678,7 @@
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -1676,7 +1691,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
@@ -1689,7 +1704,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
@@ -1702,7 +1717,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
@@ -1715,7 +1730,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>53</v>
       </c>
@@ -1728,7 +1743,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1741,7 +1756,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -1754,7 +1769,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
@@ -1767,7 +1782,7 @@
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
@@ -1780,7 +1795,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
@@ -1793,7 +1808,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -1806,7 +1821,7 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
@@ -1819,7 +1834,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
@@ -1832,7 +1847,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>13</v>
       </c>
@@ -1843,7 +1858,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>14</v>
       </c>
@@ -1856,7 +1871,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>57</v>
       </c>
@@ -1869,7 +1884,7 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>15</v>
       </c>
@@ -1882,7 +1897,7 @@
       </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -1893,7 +1908,7 @@
       </c>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1906,7 +1921,7 @@
       </c>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>34</v>
       </c>
@@ -1919,7 +1934,7 @@
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>35</v>
       </c>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>36</v>
       </c>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashish Kumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B770B5AF-7434-4D30-80CA-D4D7CAF697AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455E4671-7A69-48CC-9A5C-8B6425CB5E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1470,6 +1470,9 @@
       <c r="C56" s="6" t="s">
         <v>136</v>
       </c>
+      <c r="D56" s="3">
+        <v>1500</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Softwares.xlsx
+++ b/Softwares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashish Kumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455E4671-7A69-48CC-9A5C-8B6425CB5E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11FD967-0EC7-4D35-B182-19435F34AF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="13350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -116,9 +116,6 @@
     <t>Kundli Chakra Professional</t>
   </si>
   <si>
-    <t>Navis Work 2026</t>
-  </si>
-  <si>
     <t>Icecream Screen Recorder</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>Smart Plant 3D</t>
+  </si>
+  <si>
+    <t>Navis Work</t>
   </si>
 </sst>
 </file>
@@ -892,10 +892,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="3">
         <v>1500</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3">
         <v>1500</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3">
         <v>1500</v>
@@ -925,10 +925,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3">
         <v>1500</v>
@@ -936,10 +936,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3">
         <v>1500</v>
@@ -947,10 +947,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3">
         <v>1500</v>
@@ -958,10 +958,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="3">
         <v>1500</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3">
         <v>1500</v>
@@ -980,10 +980,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="3">
         <v>1500</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3">
         <v>1500</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3">
         <v>1500</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="3">
         <v>1500</v>
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3">
         <v>1500</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="3">
         <v>1500</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3">
         <v>1500</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3">
         <v>1500</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" s="3">
         <v>1500</v>
@@ -1082,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" s="3">
         <v>1500</v>
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="3">
         <v>1500</v>
@@ -1104,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="3">
         <v>1500</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="3">
         <v>1500</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" s="3">
         <v>1500</v>
@@ -1137,7 +1137,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3">
         <v>1500</v>
@@ -1148,7 +1148,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3">
         <v>1500</v>
@@ -1159,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26" s="3">
         <v>1500</v>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" s="3">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="3">
         <v>1500</v>
@@ -1192,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3">
         <v>1500</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="3">
         <v>1500</v>
@@ -1214,7 +1214,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" s="3">
         <v>1500</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="3">
         <v>1500</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" s="3">
         <v>1500</v>
@@ -1247,7 +1247,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="3">
         <v>1500</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="3">
         <v>1500</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36" s="3">
         <v>1500</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D37" s="3">
         <v>1500</v>
@@ -1291,7 +1291,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" s="3">
         <v>1500</v>
@@ -1302,7 +1302,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="3">
         <v>1500</v>
@@ -1313,7 +1313,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D40" s="3">
         <v>1500</v>
@@ -1340,7 +1340,7 @@
         <v>22</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3">
         <v>1500</v>
@@ -1367,7 +1367,7 @@
         <v>25</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D46" s="3">
         <v>1500</v>
@@ -1378,7 +1378,7 @@
         <v>26</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D47" s="3">
         <v>1500</v>
@@ -1389,7 +1389,7 @@
         <v>27</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D48" s="3">
         <v>1500</v>
@@ -1400,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" s="3">
         <v>1500</v>
@@ -1411,7 +1411,7 @@
         <v>29</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D50" s="3">
         <v>1500</v>
@@ -1422,7 +1422,7 @@
         <v>30</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D51" s="3">
         <v>1500</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="D52" s="3">
         <v>1500</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D53" s="3">
         <v>1500</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D54" s="3">
         <v>1500</v>
@@ -1460,15 +1460,15 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D56" s="3">
         <v>1500</v>
@@ -1562,11 +1562,11 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D2" s="4">
         <v>7500</v>
@@ -1577,11 +1577,11 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="4">
         <v>7500</v>
@@ -1592,11 +1592,11 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="4">
         <v>2500</v>
@@ -1605,11 +1605,11 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="4">
         <v>2500</v>
@@ -1618,11 +1618,11 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4">
         <v>2500</v>
@@ -1631,11 +1631,11 @@
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D7" s="4">
         <v>2500</v>
@@ -1644,11 +1644,11 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8" s="4">
         <v>2500</v>
@@ -1657,11 +1657,11 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="4">
         <v>2500</v>
@@ -1670,11 +1670,11 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D10" s="4">
         <v>2500</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" s="4">
         <v>2500</v>
@@ -1696,11 +1696,11 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="4">
         <v>2500</v>
@@ -1709,11 +1709,11 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" s="4">
         <v>2500</v>
@@ -1722,11 +1722,11 @@
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14" s="4">
         <v>2500</v>
@@ -1735,11 +1735,11 @@
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D15" s="4">
         <v>2500</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" s="4">
         <v>2500</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17" s="4">
         <v>2500</v>
@@ -1774,11 +1774,11 @@
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="4">
         <v>2500</v>
@@ -1787,11 +1787,11 @@
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" s="4">
         <v>2500</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" s="4">
         <v>2500</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="4">
         <v>2500</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D22" s="4">
         <v>2500</v>
@@ -1839,11 +1839,11 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" s="4">
         <v>2500</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D25" s="4">
         <v>2500</v>
@@ -1876,11 +1876,11 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D26" s="4">
         <v>2500</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="4">
         <v>2500</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" s="4">
         <v>2500</v>
@@ -1926,11 +1926,11 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4">
         <v>2500</v>
@@ -1939,11 +1939,11 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="4">
         <v>2500</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
